--- a/artfynd/A 10023-2023 artfynd.xlsx
+++ b/artfynd/A 10023-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 10023-2023 artfynd.xlsx
+++ b/artfynd/A 10023-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1459,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>103381060</v>
+        <v>103381061</v>
       </c>
       <c r="B9" t="n">
-        <v>95511</v>
+        <v>95522</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1475,21 +1475,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221944</v>
+        <v>221946</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lopplummer</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Huperzia selago</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Bernh. ex Schrank &amp; Mart.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>370700.5887427086</v>
+        <v>370695.5904279769</v>
       </c>
       <c r="R9" t="n">
-        <v>6943887.617758176</v>
+        <v>6943889.65689192</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1571,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>103381061</v>
+        <v>103381117</v>
       </c>
       <c r="B10" t="n">
-        <v>95522</v>
+        <v>95519</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1587,16 +1587,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221946</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1611,10 +1611,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>370695.5904279769</v>
+        <v>368020.0511410319</v>
       </c>
       <c r="R10" t="n">
-        <v>6943889.65689192</v>
+        <v>6947063.5916311</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1683,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>103381117</v>
+        <v>103381115</v>
       </c>
       <c r="B11" t="n">
-        <v>95519</v>
+        <v>96251</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1699,21 +1699,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>219790</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1723,10 +1723,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>368020.0511410319</v>
+        <v>368652.5869857551</v>
       </c>
       <c r="R11" t="n">
-        <v>6947063.5916311</v>
+        <v>6946371.89929547</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1795,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>103381115</v>
+        <v>103381055</v>
       </c>
       <c r="B12" t="n">
-        <v>96251</v>
+        <v>95519</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1811,21 +1811,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219790</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,10 +1835,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>368652.5869857551</v>
+        <v>370762.8853471844</v>
       </c>
       <c r="R12" t="n">
-        <v>6946371.89929547</v>
+        <v>6943851.533767889</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1907,7 +1907,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>103381055</v>
+        <v>103381058</v>
       </c>
       <c r="B13" t="n">
         <v>95519</v>
@@ -1947,10 +1947,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>370762.8853471844</v>
+        <v>370871.7744811371</v>
       </c>
       <c r="R13" t="n">
-        <v>6943851.533767889</v>
+        <v>6943779.059013733</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2019,10 +2019,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>103381058</v>
+        <v>103381131</v>
       </c>
       <c r="B14" t="n">
-        <v>95519</v>
+        <v>96252</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2035,21 +2035,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>223591</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2059,10 +2059,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>370871.7744811371</v>
+        <v>367660.3752438662</v>
       </c>
       <c r="R14" t="n">
-        <v>6943779.059013733</v>
+        <v>6947607.123342355</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2131,10 +2131,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>103381131</v>
+        <v>103381057</v>
       </c>
       <c r="B15" t="n">
-        <v>96252</v>
+        <v>95519</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2147,21 +2147,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>223591</v>
+        <v>221945</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2171,10 +2171,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>367660.3752438662</v>
+        <v>370833.5280635463</v>
       </c>
       <c r="R15" t="n">
-        <v>6947607.123342355</v>
+        <v>6943804.522376233</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2240,118 +2240,6 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>103381057</v>
-      </c>
-      <c r="B16" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>221945</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Lycopodium annotinum</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Bruksvallarna, Hjd</t>
-        </is>
-      </c>
-      <c r="Q16" t="n">
-        <v>370833.5280635463</v>
-      </c>
-      <c r="R16" t="n">
-        <v>6943804.522376233</v>
-      </c>
-      <c r="S16" t="n">
-        <v>10</v>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>Tännäs</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>2021-07-13</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>2021-07-13</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="inlineStr"/>
-      <c r="AW16" t="inlineStr">
-        <is>
-          <t>Brita Danielsson</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>Brita Danielsson, Anna Dahlin</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 10023-2023 artfynd.xlsx
+++ b/artfynd/A 10023-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1459,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>103381061</v>
+        <v>103381060</v>
       </c>
       <c r="B9" t="n">
-        <v>95522</v>
+        <v>95511</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1475,21 +1475,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221946</v>
+        <v>221944</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Lopplummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Huperzia selago</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh. ex Schrank &amp; Mart.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>370695.5904279769</v>
+        <v>370700.5887427086</v>
       </c>
       <c r="R9" t="n">
-        <v>6943889.65689192</v>
+        <v>6943887.617758176</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1571,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>103381117</v>
+        <v>103381061</v>
       </c>
       <c r="B10" t="n">
-        <v>95519</v>
+        <v>95522</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1587,16 +1587,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>221946</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1611,10 +1611,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>368020.0511410319</v>
+        <v>370695.5904279769</v>
       </c>
       <c r="R10" t="n">
-        <v>6947063.5916311</v>
+        <v>6943889.65689192</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1683,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>103381115</v>
+        <v>103381117</v>
       </c>
       <c r="B11" t="n">
-        <v>96251</v>
+        <v>95519</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1699,21 +1699,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219790</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1723,10 +1723,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>368652.5869857551</v>
+        <v>368020.0511410319</v>
       </c>
       <c r="R11" t="n">
-        <v>6946371.89929547</v>
+        <v>6947063.5916311</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1795,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>103381055</v>
+        <v>103381115</v>
       </c>
       <c r="B12" t="n">
-        <v>95519</v>
+        <v>96251</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1811,21 +1811,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>219790</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,10 +1835,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>370762.8853471844</v>
+        <v>368652.5869857551</v>
       </c>
       <c r="R12" t="n">
-        <v>6943851.533767889</v>
+        <v>6946371.89929547</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1907,7 +1907,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>103381058</v>
+        <v>103381055</v>
       </c>
       <c r="B13" t="n">
         <v>95519</v>
@@ -1947,10 +1947,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>370871.7744811371</v>
+        <v>370762.8853471844</v>
       </c>
       <c r="R13" t="n">
-        <v>6943779.059013733</v>
+        <v>6943851.533767889</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2019,10 +2019,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>103381131</v>
+        <v>103381058</v>
       </c>
       <c r="B14" t="n">
-        <v>96252</v>
+        <v>95519</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2035,21 +2035,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>223591</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2059,10 +2059,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>367660.3752438662</v>
+        <v>370871.7744811371</v>
       </c>
       <c r="R14" t="n">
-        <v>6947607.123342355</v>
+        <v>6943779.059013733</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2131,10 +2131,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>103381057</v>
+        <v>103381131</v>
       </c>
       <c r="B15" t="n">
-        <v>95519</v>
+        <v>96252</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2147,21 +2147,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>223591</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2171,10 +2171,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>370833.5280635463</v>
+        <v>367660.3752438662</v>
       </c>
       <c r="R15" t="n">
-        <v>6943804.522376233</v>
+        <v>6947607.123342355</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2240,6 +2240,118 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>103381057</v>
+      </c>
+      <c r="B16" t="n">
+        <v>95519</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Bruksvallarna, Hjd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>370833.5280635463</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6943804.522376233</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Brita Danielsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Brita Danielsson, Anna Dahlin</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 10023-2023 artfynd.xlsx
+++ b/artfynd/A 10023-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,60 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>103381063</v>
+        <v>126493030</v>
       </c>
       <c r="B2" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57340</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221952</v>
+        <v>100091</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Storspov</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Numenius arquata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bruksvallarna, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>370613.1832734432</v>
+        <v>367829</v>
       </c>
       <c r="R2" t="n">
-        <v>6943942.661783675</v>
+        <v>6947320</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +752,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-07-13</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-07-13</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,44 +782,39 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Brita Danielsson</t>
+          <t>Claes Elven</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Brita Danielsson, Anna Dahlin</t>
+          <t>Claes Elven, Bodil  Elve'n</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>103381107</v>
+        <v>126493099</v>
       </c>
       <c r="B3" t="n">
-        <v>57577</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57369</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208249</v>
+        <v>102961</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Drillsnäppa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Actitis hypoleucos</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -820,20 +822,32 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bruksvallarna, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>369653.5041023606</v>
+        <v>367760</v>
       </c>
       <c r="R3" t="n">
-        <v>6945619.597465838</v>
+        <v>6947455</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,22 +871,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-07-13</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-07-13</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,27 +901,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Brita Danielsson</t>
+          <t>Claes Elven</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Brita Danielsson, Anna Dahlin</t>
+          <t>Claes Elven, Bodil  Elve'n</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>103381133</v>
+        <v>103381107</v>
       </c>
       <c r="B4" t="n">
-        <v>96251</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58817</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,21 +924,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>208249</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>367668.0188529688</v>
+        <v>369653</v>
       </c>
       <c r="R4" t="n">
-        <v>6947579.187321002</v>
+        <v>6945620</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,19 +981,9 @@
           <t>2021-07-13</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-07-13</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,12 +1013,7 @@
         <v>103381109</v>
       </c>
       <c r="B5" t="n">
-        <v>57577</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58817</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1051,10 +1045,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>369081.7616234226</v>
+        <v>369082</v>
       </c>
       <c r="R5" t="n">
-        <v>6946084.467515437</v>
+        <v>6946084</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,19 +1078,9 @@
           <t>2021-07-13</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-07-13</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,15 +1107,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>103381119</v>
+        <v>103381067</v>
       </c>
       <c r="B6" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1139,21 +1118,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>219790</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>368029.8181671799</v>
+        <v>370568</v>
       </c>
       <c r="R6" t="n">
-        <v>6947030.961777103</v>
+        <v>6944091</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1196,19 +1175,9 @@
           <t>2021-07-13</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2021-07-13</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1238,12 +1207,7 @@
         <v>103381068</v>
       </c>
       <c r="B7" t="n">
-        <v>96251</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1275,10 +1239,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>370616.8942526879</v>
+        <v>370617</v>
       </c>
       <c r="R7" t="n">
-        <v>6944356.44092819</v>
+        <v>6944357</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1308,19 +1272,9 @@
           <t>2021-07-13</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2021-07-13</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,15 +1301,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>103381114</v>
+        <v>103381110</v>
       </c>
       <c r="B8" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1363,21 +1312,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221952</v>
+        <v>219790</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1336,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>368666.514180614</v>
+        <v>369331</v>
       </c>
       <c r="R8" t="n">
-        <v>6946374.110142234</v>
+        <v>6945755</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1420,19 +1369,9 @@
           <t>2021-07-13</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2021-07-13</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,15 +1398,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>103381060</v>
+        <v>103381115</v>
       </c>
       <c r="B9" t="n">
-        <v>95511</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1475,21 +1409,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221944</v>
+        <v>219790</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lopplummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Huperzia selago</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Bernh. ex Schrank &amp; Mart.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1433,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>370700.5887427086</v>
+        <v>368653</v>
       </c>
       <c r="R9" t="n">
-        <v>6943887.617758176</v>
+        <v>6946372</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1532,19 +1466,9 @@
           <t>2021-07-13</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2021-07-13</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,15 +1495,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>103381061</v>
+        <v>103381133</v>
       </c>
       <c r="B10" t="n">
-        <v>95522</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1587,21 +1506,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221946</v>
+        <v>219790</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,10 +1530,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>370695.5904279769</v>
+        <v>367668</v>
       </c>
       <c r="R10" t="n">
-        <v>6943889.65689192</v>
+        <v>6947579</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1644,19 +1563,9 @@
           <t>2021-07-13</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2021-07-13</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,15 +1592,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>103381117</v>
+        <v>103381060</v>
       </c>
       <c r="B11" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97977</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1699,23 +1603,19 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>221944</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1723,10 +1623,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>368020.0511410319</v>
+        <v>370700</v>
       </c>
       <c r="R11" t="n">
-        <v>6947063.5916311</v>
+        <v>6943888</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1756,19 +1656,9 @@
           <t>2021-07-13</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2021-07-13</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,15 +1685,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>103381115</v>
+        <v>103381055</v>
       </c>
       <c r="B12" t="n">
-        <v>96251</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1811,21 +1696,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219790</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,10 +1720,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>368652.5869857551</v>
+        <v>370763</v>
       </c>
       <c r="R12" t="n">
-        <v>6946371.89929547</v>
+        <v>6943851</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1868,19 +1753,9 @@
           <t>2021-07-13</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2021-07-13</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,15 +1782,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>103381055</v>
+        <v>103381057</v>
       </c>
       <c r="B13" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1947,10 +1817,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>370762.8853471844</v>
+        <v>370834</v>
       </c>
       <c r="R13" t="n">
-        <v>6943851.533767889</v>
+        <v>6943804</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1980,19 +1850,9 @@
           <t>2021-07-13</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2021-07-13</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2022,12 +1882,7 @@
         <v>103381058</v>
       </c>
       <c r="B14" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2059,10 +1914,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>370871.7744811371</v>
+        <v>370872</v>
       </c>
       <c r="R14" t="n">
-        <v>6943779.059013733</v>
+        <v>6943779</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2092,19 +1947,9 @@
           <t>2021-07-13</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2021-07-13</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2131,15 +1976,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>103381131</v>
+        <v>103381117</v>
       </c>
       <c r="B15" t="n">
-        <v>96252</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2147,21 +1987,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>223591</v>
+        <v>221945</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2171,10 +2011,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>367660.3752438662</v>
+        <v>368020</v>
       </c>
       <c r="R15" t="n">
-        <v>6947607.123342355</v>
+        <v>6947064</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2204,19 +2044,9 @@
           <t>2021-07-13</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2021-07-13</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2243,15 +2073,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>103381057</v>
+        <v>103381119</v>
       </c>
       <c r="B16" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2283,10 +2108,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>370833.5280635463</v>
+        <v>368030</v>
       </c>
       <c r="R16" t="n">
-        <v>6943804.522376233</v>
+        <v>6947031</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2316,19 +2141,9 @@
           <t>2021-07-13</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2021-07-13</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2352,6 +2167,491 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>103381061</v>
+      </c>
+      <c r="B17" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Bruksvallarna, Hjd</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>370696</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6943889</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Brita Danielsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Brita Danielsson, Anna Dahlin</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>103381063</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Bruksvallarna, Hjd</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>370613</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6943942</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Brita Danielsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Brita Danielsson, Anna Dahlin</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>103381114</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Bruksvallarna, Hjd</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>368667</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6946374</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Brita Danielsson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Brita Danielsson, Anna Dahlin</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>103381112</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99036</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Bruksvallarna, Hjd</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>369349</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6945746</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Brita Danielsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Brita Danielsson, Anna Dahlin</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>103381131</v>
+      </c>
+      <c r="B21" t="n">
+        <v>99036</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Bruksvallarna, Hjd</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>367661</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6947607</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Brita Danielsson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Brita Danielsson, Anna Dahlin</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 10023-2023 artfynd.xlsx
+++ b/artfynd/A 10023-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AZ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126493030</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -910,6 +920,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126493099</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1007,6 +1022,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381107</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1104,6 +1124,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381109</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1201,6 +1226,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381067</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1298,6 +1328,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381068</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1395,6 +1430,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381110</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1492,6 +1532,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381115</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1589,6 +1634,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381133</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1682,6 +1732,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381060</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1779,6 +1834,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381055</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1876,6 +1936,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381057</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1973,6 +2038,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381058</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2070,6 +2140,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381117</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2167,6 +2242,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381119</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2264,6 +2344,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381061</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2361,6 +2446,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381063</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2458,6 +2548,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381114</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2555,6 +2650,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381112</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2652,8 +2752,35 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381131</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>